--- a/results/Screener_Results.xlsx
+++ b/results/Screener_Results.xlsx
@@ -571,23 +571,23 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1806.900024414062</v>
+        <v>1355</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1806.584997558594</v>
+        <v>1340.410003662109</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>47.80013981533514</v>
+        <v>49.54384706883516</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-19.95914199158892</v>
+        <v>-14.04202419504395</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-26.04123135264442</v>
+        <v>-19.85231278059355</v>
       </c>
       <c r="G2" s="5" t="b">
         <v>1</v>
@@ -605,23 +605,23 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1351.699951171875</v>
+        <v>266</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1338.065002441406</v>
+        <v>264.05</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>49.38203172320745</v>
+        <v>50.46124619560598</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-14.94930106503398</v>
+        <v>-1.430530067663256</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>-20.7586856754531</v>
+        <v>-1.591996447211581</v>
       </c>
       <c r="G3" s="5" t="b">
         <v>1</v>
@@ -639,23 +639,23 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>544.1500244140625</v>
+        <v>2156</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>537.1125061035157</v>
+        <v>2119.370013427734</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>53.15346891469125</v>
+        <v>50.61227517354607</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-1.119530760655607</v>
+        <v>-41.9174025952484</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-1.960381448445258</v>
+        <v>-51.40850475752762</v>
       </c>
       <c r="G4" s="5" t="b">
         <v>1</v>
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1246.900024414062</v>
+        <v>1259.099975585938</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1231.974993896484</v>
+        <v>1233.979992675781</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>53.3310310495273</v>
+        <v>55.97743500093812</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-3.378925974368485</v>
+        <v>-1.584328854045907</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-6.661129821133224</v>
+        <v>-5.699907056455604</v>
       </c>
       <c r="G5" s="5" t="b">
         <v>1</v>
@@ -707,23 +707,23 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2899.5</v>
+        <v>556.6500244140625</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2738.879992675781</v>
+        <v>539.0550048828125</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>61.74069147752061</v>
+        <v>57.92488129124126</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-16.92076676666284</v>
+        <v>0.8725529548618169</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-48.11425025824195</v>
+        <v>-1.26388219633368</v>
       </c>
       <c r="G6" s="5" t="b">
         <v>1</v>
@@ -741,23 +741,23 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>438.25</v>
+        <v>2918.199951171875</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>416.4449981689453</v>
+        <v>2755.444995117187</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>68.773910096159</v>
+        <v>61.06400567845113</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.651105599446737</v>
+        <v>-6.990830004229792</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.960959582385478</v>
+        <v>-40.0114149768588</v>
       </c>
       <c r="G7" s="5" t="b">
         <v>1</v>
@@ -775,35 +775,35 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2763</v>
+        <v>441</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2974.145007324219</v>
+        <v>417.292497253418</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>17.80517804878916</v>
+        <v>67.95121387427673</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-105.0696399362746</v>
+        <v>6.581255990497823</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-90.75662564552752</v>
-      </c>
-      <c r="G8" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>1</v>
+        <v>3.727695008152529</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9740</v>
+        <v>9778</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>11017.35</v>
+        <v>10909.15</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>18.23148484154592</v>
+        <v>23.21343210930907</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-442.9604724299079</v>
+        <v>-481.5751230563365</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-280.9180608247605</v>
+        <v>-323.8198456317283</v>
       </c>
       <c r="G9" s="6" t="b">
         <v>0</v>
@@ -843,32 +843,32 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7652.5</v>
+        <v>955</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8540.5</v>
+        <v>978.717495727539</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>21.2583584308645</v>
+        <v>37.5396061143291</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-252.956045059962</v>
+        <v>-19.91030830387001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-140.4587743070121</v>
+        <v>-20.54943838494552</v>
       </c>
       <c r="G10" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="H10" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6" t="b">
-        <v>0</v>
+      <c r="H10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>1</v>
@@ -877,32 +877,32 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2870.699951171875</v>
+        <v>4825</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3105.649987792969</v>
+        <v>4898.144995117187</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>23.409981649092</v>
+        <v>39.69329891811114</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-86.60696004123429</v>
+        <v>-105.0947052425463</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-60.72250198329544</v>
+        <v>-108.4862487214365</v>
       </c>
       <c r="G11" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6" t="b">
-        <v>0</v>
+      <c r="H11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>1</v>
@@ -911,32 +911,32 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6859.5</v>
+        <v>1333</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>7270.225</v>
+        <v>1351.629992675781</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>24.12229442876374</v>
+        <v>41.96249105160302</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-209.6636699187948</v>
+        <v>-27.95402651832183</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-179.7551256843113</v>
+        <v>-28.94745538805931</v>
       </c>
       <c r="G12" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="b">
-        <v>0</v>
+      <c r="H12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>1</v>
@@ -945,32 +945,32 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>888.25</v>
+        <v>162.5700073242188</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>959.65</v>
+        <v>163.3830001831055</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>24.85398474634657</v>
+        <v>43.63600404981343</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-23.88486457144518</v>
+        <v>-3.794347381817374</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-17.57063359397509</v>
+        <v>-4.137444787607226</v>
       </c>
       <c r="G13" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="H13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" s="6" t="b">
-        <v>0</v>
+      <c r="H13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>1</v>
@@ -979,23 +979,23 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2341.699951171875</v>
+        <v>1023.400024414062</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2420.290014648438</v>
+        <v>1025.9375</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>33.68245320723928</v>
+        <v>45.28656637250279</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-47.88634583145176</v>
+        <v>-23.37787349661858</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-48.8269123168693</v>
+        <v>-25.52591950918527</v>
       </c>
       <c r="G14" s="6" t="b">
         <v>0</v>
@@ -1013,23 +1013,23 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4810</v>
+        <v>1805.099975585938</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>4908.114990234375</v>
+        <v>1810.064996337891</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>35.90410938610219</v>
+        <v>46.71186433801064</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-100.6778656683264</v>
+        <v>-19.55052055037709</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-104.984301336803</v>
+        <v>-24.8520684656642</v>
       </c>
       <c r="G15" s="6" t="b">
         <v>0</v>
@@ -1047,32 +1047,32 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1178.699951171875</v>
+        <v>1197</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1216.719995117187</v>
+        <v>1193.965002441406</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>37.24859905113757</v>
+        <v>50.9259316386642</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-24.85472533160669</v>
+        <v>6.633028665835809</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-25.02392323527114</v>
-      </c>
-      <c r="G16" s="6" t="b">
-        <v>0</v>
+        <v>8.195124377056151</v>
+      </c>
+      <c r="G16" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="H16" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="b">
-        <v>1</v>
+      <c r="I16" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>1</v>
@@ -1081,23 +1081,23 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>955.9500122070312</v>
+        <v>2796.199951171875</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>978.5899963378906</v>
+        <v>2971.205004882812</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>37.48438718196276</v>
+        <v>25.78010872994761</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-18.4582828904073</v>
+        <v>-110.1720607060261</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-19.74059822601756</v>
+        <v>-95.20294397303209</v>
       </c>
       <c r="G17" s="6" t="b">
         <v>0</v>
@@ -1105,33 +1105,33 @@
       <c r="H17" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>1</v>
+      <c r="I17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1002.349975585938</v>
+        <v>1301</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1026.844995117187</v>
+        <v>1361.734997558594</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>39.1299283145153</v>
+        <v>26.85454040190774</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-22.81747672592178</v>
+        <v>-23.28729581590551</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-23.85003757709787</v>
+        <v>-17.12692271112538</v>
       </c>
       <c r="G18" s="6" t="b">
         <v>0</v>
@@ -1139,33 +1139,33 @@
       <c r="H18" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <v>1</v>
+      <c r="I18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>161.0599975585938</v>
+        <v>2890</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>163.4109992980957</v>
+        <v>3103.209997558594</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>39.55705885857597</v>
+        <v>28.27701680750202</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.66606203070134</v>
+        <v>-90.89745096950219</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.012322315618668</v>
+        <v>-62.75415930293131</v>
       </c>
       <c r="G19" s="6" t="b">
         <v>0</v>
@@ -1173,33 +1173,33 @@
       <c r="H19" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>1</v>
+      <c r="I19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1327.900024414062</v>
+        <v>4410</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1350.664996337891</v>
+        <v>4735.410009765625</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>40.6348804833809</v>
+        <v>29.37045370818241</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-27.72006151842538</v>
+        <v>-144.0737974345957</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-28.62408924472467</v>
+        <v>-99.67223393029539</v>
       </c>
       <c r="G20" s="6" t="b">
         <v>0</v>
@@ -1207,33 +1207,33 @@
       <c r="H20" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>1</v>
+      <c r="I20" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2106.800048828125</v>
+        <v>861.6500244140625</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2116.695013427734</v>
+        <v>923.5100006103515</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>43.72558987561827</v>
+        <v>30.06889895924263</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-43.94124126818269</v>
+        <v>-31.57718543898409</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-51.16190673748466</v>
+        <v>-26.81669390713634</v>
       </c>
       <c r="G21" s="6" t="b">
         <v>0</v>
@@ -1241,36 +1241,36 @@
       <c r="H21" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I21" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <v>1</v>
+      <c r="I21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>9463.5</v>
+        <v>900.3499755859375</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9386.225</v>
+        <v>959.2950012207032</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>57.48050713753958</v>
+        <v>30.28606374867029</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>119.5526239032661</v>
+        <v>-26.01596330901987</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>162.4911509672097</v>
-      </c>
-      <c r="G22" s="5" t="b">
-        <v>1</v>
+        <v>-19.12712754886195</v>
+      </c>
+      <c r="G22" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="b">
         <v>0</v>
@@ -1278,30 +1278,30 @@
       <c r="I22" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="J22" s="8" t="n">
-        <v>1</v>
+      <c r="J22" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1707.800048828125</v>
+        <v>1168</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1806.345007324219</v>
+        <v>1252.534997558594</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>25.50110882932174</v>
+        <v>31.0497130723484</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-57.32908305134993</v>
+        <v>-22.7448923226782</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-53.56824890207338</v>
+        <v>-13.14970531615537</v>
       </c>
       <c r="G23" s="6" t="b">
         <v>0</v>
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>11300</v>
+        <v>11420</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>11939.85</v>
+        <v>11947.45</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>26.36311302720716</v>
+        <v>31.89875467714153</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-404.9315608539164</v>
+        <v>-421.2752993238537</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-385.7367571512854</v>
+        <v>-398.5116868059425</v>
       </c>
       <c r="G24" s="6" t="b">
         <v>0</v>
@@ -1353,23 +1353,23 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1302.900024414062</v>
+        <v>4895.5</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1363.324993896484</v>
+        <v>5214.125</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>26.64714804210624</v>
+        <v>32.06018969727863</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-20.63249539472076</v>
+        <v>-115.9683336696089</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-15.49722510346902</v>
+        <v>-74.88653857488259</v>
       </c>
       <c r="G25" s="6" t="b">
         <v>0</v>
@@ -1387,23 +1387,23 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>4403</v>
+        <v>1734.699951171875</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4742.29501953125</v>
+        <v>1797.950006103516</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>27.43648892538168</v>
+        <v>32.8884650357279</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-136.2866157774524</v>
+        <v>-56.09955537407632</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-95.8536997953728</v>
+        <v>-54.20124922822067</v>
       </c>
       <c r="G26" s="6" t="b">
         <v>0</v>
@@ -1421,23 +1421,23 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2567</v>
+        <v>1760</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2902.919995117188</v>
+        <v>1829.085003662109</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>29.30896858677598</v>
+        <v>33.6511169877964</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-70.47504472781202</v>
+        <v>-32.45165023997765</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-42.00323217830181</v>
+        <v>-25.57851812473461</v>
       </c>
       <c r="G27" s="6" t="b">
         <v>0</v>
@@ -1455,23 +1455,23 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>246.6499938964844</v>
+        <v>287.7999877929688</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>262.1425010681152</v>
+        <v>303.0725021362305</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>29.31812677588927</v>
+        <v>33.82089920024221</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-4.332281865863138</v>
+        <v>-5.41205638162819</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.946822383416261</v>
+        <v>-3.641290643673482</v>
       </c>
       <c r="G28" s="6" t="b">
         <v>0</v>
@@ -1489,23 +1489,23 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>942.2999877929688</v>
+        <v>221.2700042724609</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>974.0875</v>
+        <v>230.5745002746582</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>29.74770417996476</v>
+        <v>34.17226917956702</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-18.49848816740689</v>
+        <v>-3.884304694545079</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-17.43334292467485</v>
+        <v>-2.695361539943862</v>
       </c>
       <c r="G29" s="6" t="b">
         <v>0</v>
@@ -1523,23 +1523,23 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>865.0999755859375</v>
+        <v>2634.39990234375</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>924.0699981689453</v>
+        <v>2896.109985351562</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>30.43135907096625</v>
+        <v>34.21021773040519</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-29.55330443716116</v>
+        <v>-77.91103856721884</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-25.92118120921887</v>
+        <v>-46.45256062921061</v>
       </c>
       <c r="G30" s="6" t="b">
         <v>0</v>
@@ -1557,23 +1557,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>219.7299957275391</v>
+        <v>312</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>230.3874992370606</v>
+        <v>323.7850006103516</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>30.50780994749272</v>
+        <v>34.93989952448644</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.753008782194655</v>
+        <v>-4.821498035069396</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.590067946917175</v>
+        <v>-3.746909280874153</v>
       </c>
       <c r="G31" s="6" t="b">
         <v>0</v>
@@ -1591,23 +1591,23 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>285.1000061035156</v>
+        <v>1170.300048828125</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>303.7300033569336</v>
+        <v>1217.640002441406</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>30.62277950874251</v>
+        <v>35.42530511999168</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.734255666832837</v>
+        <v>-26.78985624809752</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.211361002004499</v>
+        <v>-25.11287640363432</v>
       </c>
       <c r="G32" s="6" t="b">
         <v>0</v>
@@ -1625,23 +1625,23 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>4920</v>
+        <v>173.8000030517578</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>5241.8</v>
+        <v>182.963500213623</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>30.67691947680662</v>
+        <v>35.47492785193816</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-88.33468945777076</v>
+        <v>-2.920320388702891</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-56.77360784271404</v>
+        <v>-1.51769458316433</v>
       </c>
       <c r="G33" s="6" t="b">
         <v>0</v>
@@ -1659,23 +1659,23 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>925.5499877929688</v>
+        <v>249.1499938964844</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>983.209994506836</v>
+        <v>261.9050003051758</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>30.72750619950577</v>
+        <v>35.51693808452954</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-27.96877365416265</v>
+        <v>-4.795078255286001</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-25.40370234664692</v>
+        <v>-3.203022086214777</v>
       </c>
       <c r="G34" s="6" t="b">
         <v>0</v>
@@ -1693,23 +1693,23 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>276.5499877929688</v>
+        <v>2339.10009765625</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>292.5874984741211</v>
+        <v>2416.670031738281</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>31.37744401427825</v>
+        <v>35.82990690431114</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-8.884589751629392</v>
+        <v>-54.9508469926086</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-8.704140440736438</v>
+        <v>-53.16673800694296</v>
       </c>
       <c r="G35" s="6" t="b">
         <v>0</v>
@@ -1727,23 +1727,23 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>172.6000061035156</v>
+        <v>940.4500122070312</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>183.0165000915527</v>
+        <v>983.0374969482422</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>31.63098903355224</v>
+        <v>36.89451429636592</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-2.628991290904167</v>
+        <v>-29.57541762155495</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-1.339872259026741</v>
+        <v>-26.37278785247945</v>
       </c>
       <c r="G36" s="6" t="b">
         <v>0</v>
@@ -1761,23 +1761,23 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>3643.199951171875</v>
+        <v>279.8999938964844</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>3810.1849609375</v>
+        <v>292.4049987792969</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>32.12538359840219</v>
+        <v>36.90218806815682</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>-70.69700300507475</v>
+        <v>-9.476193963921219</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>-59.47865771013998</v>
+        <v>-9.07026365050908</v>
       </c>
       <c r="G37" s="6" t="b">
         <v>0</v>
@@ -1795,23 +1795,23 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1180.599975585938</v>
+        <v>8027.5</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1254.104998779297</v>
+        <v>8539.075000000001</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>32.24097787957105</v>
+        <v>37.21574293778239</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-17.52639146522642</v>
+        <v>-243.9033630111735</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-11.33276852630189</v>
+        <v>-146.6236008887346</v>
       </c>
       <c r="G38" s="6" t="b">
         <v>0</v>
@@ -1829,23 +1829,23 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>1760.599975585938</v>
+        <v>960</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1830.125</v>
+        <v>994.0149993896484</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>33.53333300405215</v>
+        <v>37.63572507026642</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>-29.51284106190474</v>
+        <v>-25.37274044051901</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>-23.75272260032784</v>
+        <v>-23.43571660150393</v>
       </c>
       <c r="G39" s="6" t="b">
         <v>0</v>
@@ -1863,23 +1863,23 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>313.6499938964844</v>
+        <v>7050</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>324.0574996948242</v>
+        <v>7280.475</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>34.32410608679631</v>
+        <v>38.59723600713799</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-4.164195883557397</v>
+        <v>-210.4893857383058</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-3.544624178535706</v>
+        <v>-183.102207411084</v>
       </c>
       <c r="G40" s="6" t="b">
         <v>0</v>
@@ -1897,23 +1897,23 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>10572</v>
+        <v>1856.699951171875</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>10901.1</v>
+        <v>1906.295001220703</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>36.3369015019442</v>
+        <v>38.70440867989946</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>-156.0769288401916</v>
+        <v>-38.21218565039612</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>-142.4962117026942</v>
+        <v>-36.75019662619527</v>
       </c>
       <c r="G41" s="6" t="b">
         <v>0</v>
@@ -1931,23 +1931,23 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>957.6500244140625</v>
+        <v>3703.300048828125</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>993.0649993896484</v>
+        <v>3810.989978027344</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>36.78591321554623</v>
+        <v>39.54998439411673</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-25.03190971199592</v>
+        <v>-72.51322856765182</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-23.39240040367719</v>
+        <v>-60.8542534994556</v>
       </c>
       <c r="G42" s="6" t="b">
         <v>0</v>
@@ -1965,23 +1965,23 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>1194.699951171875</v>
+        <v>959.0999755859375</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1235.649993896484</v>
+        <v>974.9225006103516</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>37.76692671370787</v>
+        <v>39.89154724324525</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>-20.56510452569046</v>
+        <v>-18.58277457353768</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>-15.89873772128059</v>
+        <v>-17.96099030965231</v>
       </c>
       <c r="G43" s="6" t="b">
         <v>0</v>
@@ -1999,23 +1999,23 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>1855.400024414062</v>
+        <v>1684.599975585938</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1905.040002441406</v>
+        <v>1721.914996337891</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>37.96767031692107</v>
+        <v>41.70609404276053</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-36.496814769411</v>
+        <v>-14.04950276047362</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-35.92130333824917</v>
+        <v>-12.18436345502316</v>
       </c>
       <c r="G44" s="6" t="b">
         <v>0</v>
@@ -2033,23 +2033,23 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>1663.599975585938</v>
+        <v>10675</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1722.024993896484</v>
+        <v>10874.95</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>38.74977830863119</v>
+        <v>41.82848506260389</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>-11.97278074388123</v>
+        <v>-176.4713081523078</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>-10.47476100736421</v>
+        <v>-156.6142142102246</v>
       </c>
       <c r="G45" s="6" t="b">
         <v>0</v>
@@ -2067,23 +2067,23 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>693.7000122070312</v>
+        <v>1514.099975585938</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>719.1975006103515</v>
+        <v>1535.419995117187</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>38.76598369463608</v>
+        <v>43.01615678704934</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-4.809923830180423</v>
+        <v>-18.69718926804353</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-2.25103075842711</v>
+        <v>-15.91024486297768</v>
       </c>
       <c r="G46" s="6" t="b">
         <v>0</v>
@@ -2101,23 +2101,23 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>1501.300048828125</v>
+        <v>1216.699951171875</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1537.379998779297</v>
+        <v>1233.484997558594</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>38.91262655272313</v>
+        <v>44.44217805665735</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>-17.87402708593822</v>
+        <v>-22.15411284458855</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-14.51209031583613</v>
+        <v>-18.30389588516618</v>
       </c>
       <c r="G47" s="6" t="b">
         <v>0</v>
@@ -2135,23 +2135,23 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>255.1999969482422</v>
+        <v>411.5499877929688</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>263.5825004577637</v>
+        <v>420.4099990844726</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>39.86057495600584</v>
+        <v>45.32929072250063</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-1.698060923079538</v>
+        <v>0.1344282591167598</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-1.62970626134794</v>
+        <v>2.055962180636336</v>
       </c>
       <c r="G48" s="6" t="b">
         <v>0</v>
@@ -2169,23 +2169,23 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>406.5499877929688</v>
+        <v>707.25</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>420.4324981689453</v>
+        <v>717.7049987792968</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>40.72178422532093</v>
+        <v>45.99472623482651</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.08159458272990605</v>
+        <v>-5.146878445406401</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2.122183811358509</v>
+        <v>-3.108121846760935</v>
       </c>
       <c r="G49" s="6" t="b">
         <v>0</v>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>1682.400024414062</v>
+        <v>1761</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1766.065014648437</v>
+        <v>1768.675012207031</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>41.39994016786016</v>
+        <v>50.94297079989349</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2.974616726094609</v>
+        <v>6.930644254441631</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>12.38372019820567</v>
+        <v>13.4169094134225</v>
       </c>
       <c r="G50" s="6" t="b">
         <v>0</v>
@@ -2237,23 +2237,23 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>1174.400024414062</v>
+        <v>9340</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1192.229998779297</v>
+        <v>9398.950000000001</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>44.4735683723607</v>
+        <v>52.51711790511728</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>7.375593814492959</v>
+        <v>120.528566206418</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>8.808877851398799</v>
+        <v>168.742986210953</v>
       </c>
       <c r="G51" s="6" t="b">
         <v>0</v>

--- a/results/Screener_Results.xlsx
+++ b/results/Screener_Results.xlsx
@@ -2111,13 +2111,13 @@
         <v>1233.484997558594</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>44.44217805665735</v>
+        <v>44.44217802771638</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>-22.15411284458855</v>
+        <v>-22.15411284673814</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-18.30389588516618</v>
+        <v>-18.30389588832691</v>
       </c>
       <c r="G47" s="6" t="b">
         <v>0</v>

--- a/results/Screener_Results.xlsx
+++ b/results/Screener_Results.xlsx
@@ -649,13 +649,13 @@
         <v>2119.370013427734</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>50.61227517354607</v>
+        <v>50.61227522005106</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-41.9174025952484</v>
+        <v>-41.91740257180891</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-51.40850475752762</v>
+        <v>-51.40850472305785</v>
       </c>
       <c r="G4" s="5" t="b">
         <v>1</v>
@@ -2111,13 +2111,13 @@
         <v>1233.484997558594</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>44.44217802771638</v>
+        <v>44.44217805665735</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>-22.15411284673814</v>
+        <v>-22.15411284458855</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>-18.30389588832691</v>
+        <v>-18.30389588516618</v>
       </c>
       <c r="G47" s="6" t="b">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>420.4099990844726</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>45.32929072250063</v>
+        <v>45.32929061197584</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.1344282591167598</v>
+        <v>0.1344283270472602</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2.055962180636336</v>
+        <v>2.055962278079135</v>
       </c>
       <c r="G48" s="6" t="b">
         <v>0</v>

--- a/results/Screener_Results.xlsx
+++ b/results/Screener_Results.xlsx
@@ -555,9 +555,6 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -906,7 +903,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NIFTY 50  |  Generated 11 Oct 2026, 11:57 PM  |  Entry rule: RSI &lt; 25</t>
+          <t>NIFTY 50  |  Generated 12 Oct 2026, 01:39 AM  |  Entry rule: RSI &lt; 35</t>
         </is>
       </c>
     </row>
@@ -919,7 +916,7 @@
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Oversold (RSI &lt; 25)</t>
+          <t>Oversold (RSI &lt; 35)</t>
         </is>
       </c>
       <c r="D4" s="4" t="n"/>
@@ -1362,32 +1359,32 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>955</v>
+        <v>2796.199951171875</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>978.717495727539</v>
+        <v>2971.205004882812</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>37.5396061143291</v>
+        <v>25.78010872994761</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>-19.91030830387001</v>
+        <v>-110.1720607060261</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>-20.54943838494552</v>
+        <v>-95.20294397303209</v>
       </c>
       <c r="G18" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" s="14" t="b">
-        <v>1</v>
+      <c r="H18" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="J18" s="17" t="n">
         <v>1</v>
@@ -1396,32 +1393,32 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>1333</v>
+        <v>1301</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>1351.629992675781</v>
+        <v>1361.734997558594</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>41.96249105160302</v>
+        <v>26.85454040190774</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>-27.95402651832183</v>
+        <v>-23.28729581590551</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>-28.94745538805931</v>
+        <v>-17.12692271112538</v>
       </c>
       <c r="G19" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="14" t="b">
-        <v>1</v>
+      <c r="H19" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>1</v>
@@ -1430,32 +1427,32 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>4833</v>
+        <v>883.7999877929688</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>4915.2</v>
+        <v>989.9124969482422</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>42.20671982208532</v>
+        <v>27.74863183575825</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>-42.48461371119083</v>
+        <v>-36.93783962159307</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>-44.87547280788591</v>
+        <v>-22.61519446879682</v>
       </c>
       <c r="G20" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" s="14" t="b">
-        <v>1</v>
+      <c r="H20" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="J20" s="17" t="n">
         <v>1</v>
@@ -1464,32 +1461,32 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>1023.400024414062</v>
+        <v>2890</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>1025.9375</v>
+        <v>3103.209997558594</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>45.28656637250279</v>
+        <v>28.27701680750202</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>-23.37787349661858</v>
+        <v>-90.89745096950219</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>-25.52591950918527</v>
+        <v>-62.75415930293131</v>
       </c>
       <c r="G21" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" s="14" t="b">
-        <v>1</v>
+      <c r="H21" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>1</v>
@@ -1498,32 +1495,32 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>1805.099975585938</v>
+        <v>4410</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>1810.064996337891</v>
+        <v>4735.410009765625</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>46.71186433801064</v>
+        <v>29.37045370818241</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>-19.55052055037709</v>
+        <v>-144.0737974345957</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>-24.8520684656642</v>
+        <v>-99.67223393029539</v>
       </c>
       <c r="G22" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" s="14" t="b">
-        <v>1</v>
+      <c r="H22" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="J22" s="17" t="n">
         <v>1</v>
@@ -1532,29 +1529,29 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>1197</v>
+        <v>368.1499938964844</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1193.965002441406</v>
+        <v>388.7699966430664</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>50.9259316386642</v>
+        <v>30.06293983737243</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>6.633028665835809</v>
+        <v>-7.681807915307502</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>8.195124377056151</v>
-      </c>
-      <c r="G23" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15" t="b">
-        <v>0</v>
+        <v>-5.561801301038447</v>
+      </c>
+      <c r="G23" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="I23" s="15" t="b">
         <v>0</v>
@@ -1566,295 +1563,295 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>2796.199951171875</v>
+        <v>900.3499755859375</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>2971.205004882812</v>
+        <v>959.2950012207032</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>25.78010872994761</v>
+        <v>30.28606374867029</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>-110.1720607060261</v>
+        <v>-26.01596330901987</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>-95.20294397303209</v>
+        <v>-19.12712754886195</v>
       </c>
       <c r="G24" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="15" t="b">
-        <v>0</v>
+      <c r="H24" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="I24" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="18" t="n">
-        <v>0</v>
+      <c r="J24" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>1301</v>
+        <v>1168</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>1361.734997558594</v>
+        <v>1252.534997558594</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>26.85454040190774</v>
+        <v>31.0497130723484</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>-23.28729581590551</v>
+        <v>-22.7448923226782</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>-17.12692271112538</v>
+        <v>-13.14970531615537</v>
       </c>
       <c r="G25" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H25" s="15" t="b">
-        <v>0</v>
+      <c r="H25" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="I25" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J25" s="18" t="n">
-        <v>0</v>
+      <c r="J25" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>883.7999877929688</v>
+        <v>11420</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>989.9124969482422</v>
+        <v>11947.45</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>27.74863183575825</v>
+        <v>31.89875467714153</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>-36.93783962159307</v>
+        <v>-421.2752993238537</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>-22.61519446879682</v>
+        <v>-398.5116868059425</v>
       </c>
       <c r="G26" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="15" t="b">
-        <v>0</v>
+      <c r="H26" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="I26" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="18" t="n">
-        <v>0</v>
+      <c r="J26" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>2890</v>
+        <v>1734.699951171875</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>3103.209997558594</v>
+        <v>1797.950006103516</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>28.27701680750202</v>
+        <v>32.8884650357279</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>-90.89745096950219</v>
+        <v>-56.09955537407632</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>-62.75415930293131</v>
+        <v>-54.20124922822067</v>
       </c>
       <c r="G27" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H27" s="15" t="b">
-        <v>0</v>
+      <c r="H27" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="I27" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J27" s="18" t="n">
-        <v>0</v>
+      <c r="J27" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>4410</v>
+        <v>1760</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>4735.410009765625</v>
+        <v>1829.085003662109</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>29.37045370818241</v>
+        <v>33.6511169877964</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>-144.0737974345957</v>
+        <v>-32.45165023997765</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>-99.67223393029539</v>
+        <v>-25.57851812473461</v>
       </c>
       <c r="G28" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H28" s="15" t="b">
-        <v>0</v>
+      <c r="H28" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="I28" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J28" s="18" t="n">
-        <v>0</v>
+      <c r="J28" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>368.1499938964844</v>
+        <v>221.2700042724609</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>388.7699966430664</v>
+        <v>230.5745002746582</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>30.06293983737243</v>
+        <v>34.17226917956702</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>-7.681807915307502</v>
+        <v>-3.884304694545079</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>-5.561801301038447</v>
+        <v>-2.695361539943862</v>
       </c>
       <c r="G29" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H29" s="15" t="b">
-        <v>0</v>
+      <c r="H29" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="I29" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J29" s="18" t="n">
-        <v>0</v>
+      <c r="J29" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>900.3499755859375</v>
+        <v>2634.39990234375</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>959.2950012207032</v>
+        <v>2896.109985351562</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>30.28606374867029</v>
+        <v>34.21021773040519</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>-26.01596330901987</v>
+        <v>-77.91103856721884</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>-19.12712754886195</v>
+        <v>-46.45256062921061</v>
       </c>
       <c r="G30" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H30" s="15" t="b">
-        <v>0</v>
+      <c r="H30" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="I30" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J30" s="18" t="n">
-        <v>0</v>
+      <c r="J30" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>1168</v>
+        <v>312</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>1252.534997558594</v>
+        <v>323.7850006103516</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>31.0497130723484</v>
+        <v>34.93989952448644</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>-22.7448923226782</v>
+        <v>-4.821498035069396</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>-13.14970531615537</v>
+        <v>-3.746909280874153</v>
       </c>
       <c r="G31" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="H31" s="15" t="b">
-        <v>0</v>
+      <c r="H31" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="I31" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J31" s="18" t="n">
-        <v>0</v>
+      <c r="J31" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>11420</v>
+        <v>955</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>11947.45</v>
+        <v>978.717495727539</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>31.89875467714153</v>
+        <v>37.5396061143291</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>-421.2752993238537</v>
+        <v>-19.91030830387001</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>-398.5116868059425</v>
+        <v>-20.54943838494552</v>
       </c>
       <c r="G32" s="15" t="b">
         <v>0</v>
@@ -1862,33 +1859,33 @@
       <c r="H32" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I32" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" s="18" t="n">
-        <v>0</v>
+      <c r="I32" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>1734.699951171875</v>
+        <v>1333</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1797.950006103516</v>
+        <v>1351.629992675781</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>32.8884650357279</v>
+        <v>41.96249105160302</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>-56.09955537407632</v>
+        <v>-27.95402651832183</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>-54.20124922822067</v>
+        <v>-28.94745538805931</v>
       </c>
       <c r="G33" s="15" t="b">
         <v>0</v>
@@ -1896,33 +1893,33 @@
       <c r="H33" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I33" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" s="18" t="n">
-        <v>0</v>
+      <c r="I33" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>1760</v>
+        <v>4833</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>1829.085003662109</v>
+        <v>4915.2</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>33.6511169877964</v>
+        <v>42.20671982208532</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>-32.45165023997765</v>
+        <v>-42.48461371119083</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>-25.57851812473461</v>
+        <v>-44.87547280788591</v>
       </c>
       <c r="G34" s="15" t="b">
         <v>0</v>
@@ -1930,33 +1927,33 @@
       <c r="H34" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I34" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" s="18" t="n">
-        <v>0</v>
+      <c r="I34" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>221.2700042724609</v>
+        <v>1023.400024414062</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>230.5745002746582</v>
+        <v>1025.9375</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>34.17226917956702</v>
+        <v>45.28656637250279</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>-3.884304694545079</v>
+        <v>-23.37787349661858</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>-2.695361539943862</v>
+        <v>-25.52591950918527</v>
       </c>
       <c r="G35" s="15" t="b">
         <v>0</v>
@@ -1964,33 +1961,33 @@
       <c r="H35" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I35" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" s="18" t="n">
-        <v>0</v>
+      <c r="I35" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>2634.39990234375</v>
+        <v>1805.099975585938</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>2896.109985351562</v>
+        <v>1810.064996337891</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>34.21021773040519</v>
+        <v>46.71186433801064</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>-77.91103856721884</v>
+        <v>-19.55052055037709</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>-46.45256062921061</v>
+        <v>-24.8520684656642</v>
       </c>
       <c r="G36" s="15" t="b">
         <v>0</v>
@@ -1998,36 +1995,36 @@
       <c r="H36" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I36" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" s="18" t="n">
-        <v>0</v>
+      <c r="I36" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>312</v>
+        <v>1197</v>
       </c>
       <c r="C37" s="12" t="n">
-        <v>323.7850006103516</v>
+        <v>1193.965002441406</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>34.93989952448644</v>
+        <v>50.9259316386642</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>-4.821498035069396</v>
+        <v>6.633028665835809</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>-3.746909280874153</v>
-      </c>
-      <c r="G37" s="15" t="b">
-        <v>0</v>
+        <v>8.195124377056151</v>
+      </c>
+      <c r="G37" s="14" t="b">
+        <v>1</v>
       </c>
       <c r="H37" s="15" t="b">
         <v>0</v>
@@ -2035,8 +2032,8 @@
       <c r="I37" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J37" s="18" t="n">
-        <v>0</v>
+      <c r="J37" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2825,7 +2822,7 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
